--- a/tests/testdata/excel/ファイル名/長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前.xlsx
+++ b/tests/testdata/excel/ファイル名/長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A1F9787-D63F-48BA-B62B-FE0C30D7487F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBF1FAA3-7C89-4993-A498-0F21D2C8F7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{798BF3AA-21D9-4E2E-8DCB-F9502B25C5F7}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{ACE4B260-098A-49FB-A7F0-EA071065A766}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DEAE794-89FB-4C30-B54A-77F77EBC2B5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA218538-28E7-48C6-AE19-B289FBA1AEA9}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前.xlsx
+++ b/tests/testdata/excel/ファイル名/長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前長い名前.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBF1FAA3-7C89-4993-A498-0F21D2C8F7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{41F09F24-1817-43FE-AC13-2CAE6EBB0E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{ACE4B260-098A-49FB-A7F0-EA071065A766}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{35385E67-D9CA-42DB-A153-13E16A1864E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA218538-28E7-48C6-AE19-B289FBA1AEA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA07797F-3A7F-46D9-88A3-F0A491B2BA80}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
